--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_27-10-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_27-10-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC07D4D5-8F27-46D6-9402-DB7D7D35B237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1462FC08-46F3-41FF-B312-6E94A2919B36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30480" yWindow="135" windowWidth="21600" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4665" yWindow="1515" windowWidth="21600" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -478,12 +478,6 @@
     <t>£69.02</t>
   </si>
   <si>
-    <t>£117.75</t>
-  </si>
-  <si>
-    <t>£119.36</t>
-  </si>
-  <si>
     <t>£566.26</t>
   </si>
   <si>
@@ -836,6 +830,12 @@
   </si>
   <si>
     <t>£55.00</t>
+  </si>
+  <si>
+    <t>£588.75</t>
+  </si>
+  <si>
+    <t>£596.8</t>
   </si>
 </sst>
 </file>
@@ -1279,7 +1279,7 @@
         <v>66</v>
       </c>
       <c r="F2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G2" t="s">
         <v>89</v>
@@ -1291,7 +1291,7 @@
         <v>124</v>
       </c>
       <c r="J2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="K2" t="s">
         <v>139</v>
@@ -1300,22 +1300,22 @@
         <v>88</v>
       </c>
       <c r="M2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="N2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="O2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Q2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="R2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -1335,7 +1335,7 @@
         <v>67</v>
       </c>
       <c r="F3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G3" t="s">
         <v>90</v>
@@ -1347,7 +1347,7 @@
         <v>125</v>
       </c>
       <c r="J3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="K3" t="s">
         <v>140</v>
@@ -1356,22 +1356,22 @@
         <v>88</v>
       </c>
       <c r="M3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="N3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="O3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="P3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Q3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="R3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -1391,7 +1391,7 @@
         <v>88</v>
       </c>
       <c r="F4" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G4" t="s">
         <v>91</v>
@@ -1403,7 +1403,7 @@
         <v>126</v>
       </c>
       <c r="J4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="K4" t="s">
         <v>141</v>
@@ -1412,22 +1412,22 @@
         <v>88</v>
       </c>
       <c r="M4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="N4" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="O4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="P4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Q4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="R4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -1447,7 +1447,7 @@
         <v>69</v>
       </c>
       <c r="F5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G5" t="s">
         <v>92</v>
@@ -1459,7 +1459,7 @@
         <v>127</v>
       </c>
       <c r="J5" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="K5" t="s">
         <v>142</v>
@@ -1468,22 +1468,22 @@
         <v>88</v>
       </c>
       <c r="M5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="N5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="O5" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="P5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Q5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="R5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -1503,7 +1503,7 @@
         <v>70</v>
       </c>
       <c r="F6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G6" t="s">
         <v>93</v>
@@ -1515,7 +1515,7 @@
         <v>128</v>
       </c>
       <c r="J6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="K6" t="s">
         <v>143</v>
@@ -1524,22 +1524,22 @@
         <v>88</v>
       </c>
       <c r="M6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="N6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="O6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="P6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Q6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="R6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -1559,7 +1559,7 @@
         <v>71</v>
       </c>
       <c r="F7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G7" t="s">
         <v>72</v>
@@ -1571,7 +1571,7 @@
         <v>129</v>
       </c>
       <c r="J7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="K7" t="s">
         <v>144</v>
@@ -1580,22 +1580,22 @@
         <v>88</v>
       </c>
       <c r="M7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="N7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="O7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="P7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Q7" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="R7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -1615,7 +1615,7 @@
         <v>72</v>
       </c>
       <c r="F8" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G8" t="s">
         <v>94</v>
@@ -1627,7 +1627,7 @@
         <v>130</v>
       </c>
       <c r="J8" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="K8" t="s">
         <v>145</v>
@@ -1636,22 +1636,22 @@
         <v>88</v>
       </c>
       <c r="M8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="N8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="O8" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="P8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Q8" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="R8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -1671,7 +1671,7 @@
         <v>73</v>
       </c>
       <c r="F9" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G9" t="s">
         <v>95</v>
@@ -1683,7 +1683,7 @@
         <v>131</v>
       </c>
       <c r="J9" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="K9" t="s">
         <v>146</v>
@@ -1692,22 +1692,22 @@
         <v>88</v>
       </c>
       <c r="M9" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N9" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="O9" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="P9" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Q9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="R9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -1727,7 +1727,7 @@
         <v>74</v>
       </c>
       <c r="F10" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G10" t="s">
         <v>96</v>
@@ -1739,7 +1739,7 @@
         <v>132</v>
       </c>
       <c r="J10" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="K10" t="s">
         <v>146</v>
@@ -1751,19 +1751,19 @@
         <v>88</v>
       </c>
       <c r="N10" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="O10" t="s">
         <v>74</v>
       </c>
       <c r="P10" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Q10" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="R10" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -1783,7 +1783,7 @@
         <v>75</v>
       </c>
       <c r="F11" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G11" t="s">
         <v>97</v>
@@ -1795,7 +1795,7 @@
         <v>133</v>
       </c>
       <c r="J11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="K11" t="s">
         <v>147</v>
@@ -1804,22 +1804,22 @@
         <v>88</v>
       </c>
       <c r="M11" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="N11" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="O11" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="P11" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Q11" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="R11" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -1839,7 +1839,7 @@
         <v>88</v>
       </c>
       <c r="F12" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G12" t="s">
         <v>98</v>
@@ -1851,7 +1851,7 @@
         <v>134</v>
       </c>
       <c r="J12" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K12" t="s">
         <v>88</v>
@@ -1860,19 +1860,19 @@
         <v>88</v>
       </c>
       <c r="M12" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="N12" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="O12" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="P12" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Q12" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="R12" t="s">
         <v>88</v>
@@ -1895,7 +1895,7 @@
         <v>77</v>
       </c>
       <c r="F13" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G13" t="s">
         <v>99</v>
@@ -1907,7 +1907,7 @@
         <v>135</v>
       </c>
       <c r="J13" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="K13" t="s">
         <v>148</v>
@@ -1916,22 +1916,22 @@
         <v>88</v>
       </c>
       <c r="M13" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="N13" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="O13" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="P13" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Q13" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="R13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -1951,7 +1951,7 @@
         <v>88</v>
       </c>
       <c r="F14" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="G14" t="s">
         <v>100</v>
@@ -1963,7 +1963,7 @@
         <v>136</v>
       </c>
       <c r="J14" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="K14" t="s">
         <v>149</v>
@@ -1972,19 +1972,19 @@
         <v>88</v>
       </c>
       <c r="M14" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="N14" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O14" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="P14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Q14" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="R14" t="s">
         <v>88</v>
@@ -2007,7 +2007,7 @@
         <v>88</v>
       </c>
       <c r="F15" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G15" t="s">
         <v>101</v>
@@ -2019,7 +2019,7 @@
         <v>137</v>
       </c>
       <c r="J15" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="K15" t="s">
         <v>150</v>
@@ -2028,19 +2028,19 @@
         <v>88</v>
       </c>
       <c r="M15" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="N15" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="O15" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="P15" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Q15" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="R15" t="s">
         <v>88</v>
@@ -2063,7 +2063,7 @@
         <v>80</v>
       </c>
       <c r="F16" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G16" t="s">
         <v>102</v>
@@ -2075,7 +2075,7 @@
         <v>138</v>
       </c>
       <c r="J16" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="K16" t="s">
         <v>151</v>
@@ -2084,22 +2084,22 @@
         <v>88</v>
       </c>
       <c r="M16" t="s">
+        <v>166</v>
+      </c>
+      <c r="N16" t="s">
+        <v>231</v>
+      </c>
+      <c r="O16" t="s">
+        <v>181</v>
+      </c>
+      <c r="P16" t="s">
         <v>168</v>
-      </c>
-      <c r="N16" t="s">
-        <v>233</v>
-      </c>
-      <c r="O16" t="s">
-        <v>183</v>
-      </c>
-      <c r="P16" t="s">
-        <v>170</v>
       </c>
       <c r="Q16" t="s">
         <v>120</v>
       </c>
       <c r="R16" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
@@ -2110,10 +2110,10 @@
         <v>57</v>
       </c>
       <c r="C17" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D17" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E17" t="s">
         <v>88</v>
@@ -2187,7 +2187,7 @@
         <v>88</v>
       </c>
       <c r="J18" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="K18" t="s">
         <v>88</v>
@@ -2199,13 +2199,13 @@
         <v>88</v>
       </c>
       <c r="N18" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="O18" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="P18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Q18" t="s">
         <v>88</v>
@@ -2243,7 +2243,7 @@
         <v>88</v>
       </c>
       <c r="J19" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="K19" t="s">
         <v>88</v>
@@ -2255,19 +2255,19 @@
         <v>88</v>
       </c>
       <c r="N19" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="O19" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="P19" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Q19" t="s">
         <v>88</v>
       </c>
       <c r="R19" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -2299,7 +2299,7 @@
         <v>88</v>
       </c>
       <c r="J20" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K20" t="s">
         <v>88</v>
@@ -2355,7 +2355,7 @@
         <v>88</v>
       </c>
       <c r="J21" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="K21" t="s">
         <v>88</v>
@@ -2411,7 +2411,7 @@
         <v>88</v>
       </c>
       <c r="J22" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="K22" t="s">
         <v>88</v>
@@ -2461,7 +2461,7 @@
         <v>105</v>
       </c>
       <c r="H23" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I23" t="s">
         <v>88</v>
@@ -2470,19 +2470,19 @@
         <v>88</v>
       </c>
       <c r="K23" t="s">
-        <v>152</v>
+        <v>270</v>
       </c>
       <c r="L23" t="s">
         <v>88</v>
       </c>
       <c r="M23" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="N23" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="O23" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="P23" t="s">
         <v>88</v>
@@ -2491,7 +2491,7 @@
         <v>88</v>
       </c>
       <c r="R23" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -2526,19 +2526,19 @@
         <v>88</v>
       </c>
       <c r="K24" t="s">
-        <v>153</v>
+        <v>271</v>
       </c>
       <c r="L24" t="s">
         <v>88</v>
       </c>
       <c r="M24" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="N24" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="O24" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="P24" t="s">
         <v>88</v>
@@ -2547,7 +2547,7 @@
         <v>88</v>
       </c>
       <c r="R24" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -2582,19 +2582,19 @@
         <v>88</v>
       </c>
       <c r="K25" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="L25" t="s">
         <v>88</v>
       </c>
       <c r="M25" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="N25" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="O25" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="P25" t="s">
         <v>88</v>
@@ -2603,7 +2603,7 @@
         <v>88</v>
       </c>
       <c r="R25" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
